--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487955_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487955_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1028</v>
+        <v>5.4992</v>
       </c>
       <c r="E2" t="n">
-        <v>8.616199999999999</v>
+        <v>7.479</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5134</v>
+        <v>-1.9799</v>
       </c>
       <c r="G2" t="n">
         <v>3.6618</v>
@@ -610,13 +610,13 @@
         <v>0.5947</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9762</v>
+        <v>0.3726</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7806</v>
+        <v>0.6434</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8044</v>
+        <v>-0.2709</v>
       </c>
       <c r="V2" t="n">
         <v>0.8701</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MIR AMATE</t>
+          <t>P. LOZANO CID</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5929</v>
+        <v>0.343</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5903</v>
+        <v>-0.0222</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0025</v>
+        <v>0.3652</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5214</v>
+        <v>0.4477</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2746</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2468</v>
+        <v>0.4477</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0765</v>
+        <v>0.0402</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1211</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1975</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5551</v>
+        <v>0.4075</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3957</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9508</v>
+        <v>0.4075</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9412</v>
+        <v>-0.1046</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7967</v>
+        <v>-0.0624</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1445</v>
+        <v>-0.0422</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0252</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. LOZANO CID</t>
+          <t>A. MIR AMATE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2869</v>
+        <v>-0.1639</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0222</v>
+        <v>0.002</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3091</v>
+        <v>-0.1659</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4477</v>
+        <v>-0.5214</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0.2746</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4477</v>
+        <v>-0.2468</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0402</v>
+        <v>-1.0765</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>-1.1975</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4075</v>
+        <v>0.5551</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.3957</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4075</v>
+        <v>0.9508</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1608</v>
+        <v>0.1844</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0624</v>
+        <v>0.2084</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0984</v>
+        <v>-0.024</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.0252</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8953</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. LOPEZ TORRE</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9681</v>
+        <v>-0.7965</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5655</v>
+        <v>3.4986</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4026</v>
+        <v>-4.2951</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2313</v>
+        <v>2.7852</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.312</v>
+        <v>-0.8155</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5433</v>
+        <v>3.6007</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3159</v>
+        <v>4.2194</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3159</v>
+        <v>0.5114</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.708</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5472</v>
+        <v>-1.4342</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0039</v>
+        <v>-1.3269</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5433</v>
+        <v>-0.1073</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1982</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1905</v>
+        <v>-0.3405</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2496</v>
+        <v>0.0038</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0591</v>
+        <v>-0.3443</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2071</v>
+        <v>-3.0429</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2071</v>
+        <v>-3.3095</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. TAVIO SOLIS</t>
+          <t>G. LOPEZ TORRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2881</v>
+        <v>-0.8776</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1912</v>
+        <v>-0.5031</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4792</v>
+        <v>-0.3745</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2313</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4474</v>
+        <v>-0.312</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5459</v>
+        <v>0.5433</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5545</v>
+        <v>-0.3159</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5782</v>
+        <v>-0.3159</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1328</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.456</v>
+        <v>0.5472</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8691</v>
+        <v>0.0039</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4132</v>
+        <v>0.5433</v>
       </c>
       <c r="P7" t="n">
         <v>0.1982</v>
@@ -1000,13 +1000,13 @@
         <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3777</v>
+        <v>-0.1001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3634</v>
+        <v>-0.1872</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0144</v>
+        <v>0.0871</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2071</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>H. TAVIO SOLIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9952</v>
+        <v>-1.0333</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4965</v>
+        <v>0.4178</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.4916</v>
+        <v>-1.4511</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7852</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8155</v>
+        <v>-1.4474</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6007</v>
+        <v>1.5459</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2194</v>
+        <v>0.5545</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5114</v>
+        <v>-0.5782</v>
       </c>
       <c r="L8" t="n">
-        <v>3.708</v>
+        <v>1.1328</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4342</v>
+        <v>-0.456</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3269</v>
+        <v>-0.8691</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1073</v>
+        <v>0.4132</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1982</v>
+        <v>0.1982</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5392</v>
+        <v>-0.123</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9984</v>
+        <v>-0.1367</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5409</v>
+        <v>0.0137</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.0429</v>
+        <v>-1.2071</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.3095</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>Z. POPE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3086</v>
+        <v>-2.6066</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.462</v>
+        <v>1.3843</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1534</v>
+        <v>-3.9909</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9369</v>
+        <v>-1.1474</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.2396</v>
+        <v>-0.9484</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3028</v>
+        <v>-0.1991</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7583</v>
+        <v>1.1135</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6422</v>
+        <v>0.3903</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8839</v>
+        <v>0.7232</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1786</v>
+        <v>-2.2609</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5975</v>
+        <v>-1.3386</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4189</v>
+        <v>-0.9223</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7744</v>
+        <v>0.1532</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7453</v>
+        <v>0.2708</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0291</v>
+        <v>-0.1176</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3621</v>
+        <v>-1.8107</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8953</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Z. POPE</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8913</v>
+        <v>-2.7482</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8749</v>
+        <v>-1.1483</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7663</v>
+        <v>-1.5999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1474</v>
+        <v>0.8106</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9484</v>
+        <v>0.849</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1991</v>
+        <v>-0.0384</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1135</v>
+        <v>1.325</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3903</v>
+        <v>1.2447</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7232</v>
+        <v>0.0804</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2609</v>
+        <v>-0.5144</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3386</v>
+        <v>-0.3957</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9223</v>
+        <v>-0.1187</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1982</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1315</v>
+        <v>0.1294</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2386</v>
+        <v>-0.1541</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1071</v>
+        <v>0.2835</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8107</v>
+        <v>-2.1024</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8107</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0278</v>
+        <v>-3.0405</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6806</v>
+        <v>-2.7447</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3472</v>
+        <v>-0.2958</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8106</v>
+        <v>-1.9369</v>
       </c>
       <c r="H11" t="n">
-        <v>0.849</v>
+        <v>-3.2396</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0384</v>
+        <v>1.3028</v>
       </c>
       <c r="J11" t="n">
-        <v>1.325</v>
+        <v>-1.7583</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2447</v>
+        <v>-2.6422</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0804</v>
+        <v>0.8839</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5144</v>
+        <v>-0.1786</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3957</v>
+        <v>-0.5975</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1187</v>
+        <v>0.4189</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5858</v>
+        <v>-1.784</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1502</v>
+        <v>1.0425</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6864</v>
+        <v>0.4626</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5362</v>
+        <v>0.5798</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1024</v>
+        <v>-0.3621</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.337</v>
+        <v>0.5331</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7654</v>
+        <v>-0.8953</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9329</v>
+        <v>-4.1875</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9872</v>
+        <v>0.7045</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9201</v>
+        <v>-4.892</v>
       </c>
       <c r="G12" t="n">
         <v>0.5556</v>
@@ -1390,13 +1390,13 @@
         <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3748</v>
+        <v>0.1202</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.3378</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2457</v>
+        <v>-0.2176</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4846</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.2324</v>
+        <v>-9.8019</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.1707</v>
+        <v>-6.9648</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0616</v>
+        <v>-2.837</v>
       </c>
       <c r="G13" t="n">
         <v>-3.6094</v>
@@ -1468,13 +1468,13 @@
         <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5719</v>
+        <v>-0.1413</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0497</v>
+        <v>0.1562</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5221</v>
+        <v>-0.2975</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6991000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.3405</v>
+        <v>-16.0925</v>
       </c>
       <c r="E14" t="n">
-        <v>4.176599999999999</v>
+        <v>5.424399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-21.517</v>
+        <v>-21.5169</v>
       </c>
       <c r="G14" t="n">
         <v>4.697</v>
@@ -1525,7 +1525,7 @@
         <v>6.595200000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8931</v>
+        <v>7.893100000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-9.7912</v>
@@ -1546,13 +1546,13 @@
         <v>3.9644</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.05519999999999992</v>
+        <v>1.1928</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2946</v>
+        <v>1.5426</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3499000000000002</v>
+        <v>-0.35</v>
       </c>
       <c r="V14" t="n">
         <v>-12.0711</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.957000000000001</v>
+        <v>10.3736</v>
       </c>
       <c r="E15" t="n">
         <v>12.6818</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7248</v>
+        <v>-2.3082</v>
       </c>
       <c r="G15" t="n">
         <v>4.0489</v>
@@ -1624,13 +1624,13 @@
         <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9801</v>
+        <v>-0.5635</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1724</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8077</v>
+        <v>-0.3911</v>
       </c>
       <c r="V15" t="n">
         <v>4.7077</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.4779</v>
+        <v>6.0296</v>
       </c>
       <c r="E16" t="n">
-        <v>8.587400000000001</v>
+        <v>7.0594</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1095</v>
+        <v>-1.0298</v>
       </c>
       <c r="G16" t="n">
         <v>2.0121</v>
@@ -1702,13 +1702,13 @@
         <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8531</v>
+        <v>0.4047</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9898</v>
+        <v>0.4618</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1367</v>
+        <v>-0.0571</v>
       </c>
       <c r="V16" t="n">
         <v>2.0269</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.846</v>
+        <v>4.5066</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9469</v>
+        <v>3.7244</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8991</v>
+        <v>0.7822</v>
       </c>
       <c r="G17" t="n">
         <v>3.7546</v>
@@ -1780,13 +1780,13 @@
         <v>0.9911</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8248</v>
+        <v>0.4855</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8099</v>
+        <v>0.5874</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0149</v>
+        <v>-0.102</v>
       </c>
       <c r="V17" t="n">
         <v>0.2666</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8574</v>
+        <v>3.5882</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1175</v>
+        <v>2.9325</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7399</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5492</v>
@@ -1858,13 +1858,13 @@
         <v>2.3787</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7891</v>
+        <v>0.0259</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1162</v>
+        <v>0.032</v>
       </c>
       <c r="V18" t="n">
         <v>2.7009</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6144</v>
+        <v>2.0643</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3065</v>
+        <v>1.1214</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3079</v>
+        <v>0.9429</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3378</v>
@@ -1936,13 +1936,13 @@
         <v>1.9822</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2117</v>
+        <v>0.6616</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6864</v>
+        <v>0.1286</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8981</v>
+        <v>0.533</v>
       </c>
       <c r="V19" t="n">
         <v>0.7494</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7301</v>
+        <v>-0.539</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.301</v>
+        <v>-1.6988</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4291</v>
+        <v>1.1598</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5465</v>
+        <v>-2.8334</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4164</v>
+        <v>-1.7717</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1301</v>
+        <v>-1.0617</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6791</v>
+        <v>-1.7875</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6791</v>
+        <v>-1.1161</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.6713</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-1.046</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7372</v>
+        <v>-0.6556</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1301</v>
+        <v>-0.3904</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6182</v>
+        <v>0.0276</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3782</v>
+        <v>-0.1779</v>
       </c>
       <c r="U21" t="n">
-        <v>0.24</v>
+        <v>0.2055</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.4828</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.2163</v>
       </c>
     </row>
     <row r="22">
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5107</v>
+        <v>-1.306</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.31</v>
+        <v>-0.7084</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7993</v>
+        <v>-0.5976</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8334</v>
+        <v>-1.5465</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7717</v>
+        <v>-1.4164</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0617</v>
+        <v>-0.1301</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7875</v>
+        <v>-0.6791</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1161</v>
+        <v>-0.6791</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6713</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.046</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6556</v>
+        <v>-0.7372</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3904</v>
+        <v>-0.1301</v>
       </c>
       <c r="P23" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9441000000000001</v>
+        <v>0.0422</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7891</v>
+        <v>-0.0293</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.155</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4828</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.617</v>
+        <v>-1.7472</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7323</v>
+        <v>-2.223</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1153</v>
+        <v>0.4758</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6568</v>
@@ -2326,13 +2326,13 @@
         <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8303</v>
+        <v>0.0395</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7267</v>
+        <v>-0.2174</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1036</v>
+        <v>0.2568</v>
       </c>
       <c r="V24" t="n">
         <v>1.4737</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1598</v>
+        <v>-3.5558</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3923</v>
+        <v>-0.9848</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7676</v>
+        <v>-2.571</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1852</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0252</v>
+        <v>-0.4212</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6643</v>
+        <v>-0.2568</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3609</v>
+        <v>-0.1644</v>
       </c>
       <c r="V25" t="n">
         <v>-0.337</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>17.3404</v>
+        <v>18.0196</v>
       </c>
       <c r="E26" t="n">
-        <v>20.91340000000001</v>
+        <v>20.9134</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.573099999999999</v>
+        <v>-2.8938</v>
       </c>
       <c r="G26" t="n">
         <v>-4.696899999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3956</v>
+        <v>3.395599999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-8.092500000000001</v>
@@ -2458,10 +2458,10 @@
         <v>9.7911</v>
       </c>
       <c r="K26" t="n">
-        <v>9.9907</v>
+        <v>9.990699999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.1995999999999993</v>
+        <v>-0.1996000000000002</v>
       </c>
       <c r="M26" t="n">
         <v>-14.4883</v>
@@ -2482,13 +2482,13 @@
         <v>13.8757</v>
       </c>
       <c r="S26" t="n">
-        <v>0.05519999999999947</v>
+        <v>0.7342</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3499000000000002</v>
+        <v>0.3499</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2946999999999998</v>
+        <v>0.3842</v>
       </c>
       <c r="V26" t="n">
         <v>12.071</v>
